--- a/samples/survey_ems2.xlsx
+++ b/samples/survey_ems2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV28"/>
+  <dimension ref="A1:AW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,53 @@
           <t>구급 전문역량 심화과정 2기 설문 결과(모의)</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -431,235 +478,240 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>소속 기관</t>
+          <t>소속</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>현재 계급</t>
+          <t>근무기간</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>보직</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>심폐소생술·응급처치 | 박한울 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>심폐소생술·응급처치 | 박한울 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>심폐소생술·응급처치 | 박한울 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>심폐소생술·응급처치 | 박한울 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>심폐소생술·응급처치 | 박한울 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>기본소생술(BLS) 실습 | 오나래 강사 | 태도: 교수님은 성실한 자세로 노력하며 강의(훈련)하였나요?</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>기본소생술(BLS) 실습 | 오나래 강사 | 준비성: 훈련환경은 적절하고 장비는 충분했나요?</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>기본소생술(BLS) 실습 | 오나래 강사 | 전문성: 교수님은 전문적이고 숙달된 자세로 훈련을 지도했나요?</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>기본소생술(BLS) 실습 | 오나래 강사 | 적용성: 재난현장 및 실무에서 활용할 수 있는 훈련인가요?</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>기본소생술(BLS) 실습 | 오나래 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>외상환자 처치 | 오참솔 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>외상환자 처치 | 오참솔 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>외상환자 처치 | 오참솔 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>외상환자 처치 | 오참솔 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>외상환자 처치 | 오참솔 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>병원 전 외상 응급처치 | 한슬기 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>병원 전 외상 응급처치 | 한슬기 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>병원 전 외상 응급처치 | 한슬기 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>병원 전 외상 응급처치 | 한슬기 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>병원 전 외상 응급처치 | 한슬기 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>감염관리 | 윤마루 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>감염관리 | 윤마루 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>감염관리 | 윤마루 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>감염관리 | 윤마루 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>감염관리 | 윤마루 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>구급차 운용 안전 | 박이든 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>구급차 운용 안전 | 박이든 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>구급차 운용 안전 | 박이든 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>구급차 운용 안전 | 박이든 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>구급차 운용 안전 | 박이든 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>응급차량 안전운전 | 오소담 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>응급차량 안전운전 | 오소담 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>응급차량 안전운전 | 오소담 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>응급차량 안전운전 | 오소담 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>응급차량 안전운전 | 오소담 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교재의 품질</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 강의실 및 교육기자재</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 편의시설</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교직원의 친절도</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 구내식당 이용</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 음식의 간</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 메뉴의 다양성</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 청결도</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>공통 | 과정 운영 | 의견: 이번 과정 운영(일정·시설·안내 등)에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
@@ -673,17 +725,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -703,14 +755,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -723,36 +775,36 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -760,23 +812,23 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -786,15 +838,15 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -807,27 +859,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -835,20 +887,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -858,17 +910,17 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -878,10 +930,15 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>식당 대기 시간이 길었음</t>
         </is>
@@ -900,12 +957,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -923,20 +980,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -944,12 +1001,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -957,7 +1014,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -965,12 +1022,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -978,20 +1035,20 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -999,20 +1056,20 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1028,15 +1085,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1049,12 +1106,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1062,12 +1119,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1077,25 +1134,30 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
@@ -1114,12 +1176,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1129,7 +1191,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1139,17 +1201,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1159,23 +1221,23 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1183,12 +1245,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1196,28 +1258,28 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1227,38 +1289,38 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1268,22 +1330,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1293,17 +1355,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1313,15 +1375,20 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1336,12 +1403,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1351,24 +1418,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1384,12 +1451,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1397,45 +1464,45 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1453,17 +1520,17 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1473,22 +1540,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1503,17 +1570,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1523,12 +1590,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1538,7 +1605,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -1552,6 +1619,11 @@
         </is>
       </c>
       <c r="AV6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
         <is>
           <t>5일 과정이라 실습까지 충분히 해 볼 수 있었음</t>
         </is>
@@ -1570,39 +1642,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1615,15 +1687,15 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1631,7 +1703,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1639,12 +1711,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1660,20 +1732,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1681,12 +1753,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1699,15 +1771,15 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1715,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1723,15 +1795,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1741,12 +1813,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1756,12 +1828,12 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1769,7 +1841,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1779,22 +1856,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1804,15 +1881,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1828,15 +1905,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1846,18 +1923,18 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1867,23 +1944,23 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1891,15 +1968,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1912,15 +1989,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1930,23 +2007,23 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1976,10 +2053,15 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1989,17 +2071,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2017,20 +2099,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2040,14 +2122,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2063,20 +2145,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -2084,12 +2166,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2102,15 +2184,15 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2126,36 +2208,36 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -2165,12 +2247,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2185,15 +2267,20 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2203,17 +2290,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2228,15 +2315,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2249,15 +2336,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2273,12 +2360,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2286,20 +2373,20 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2307,24 +2394,24 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2332,20 +2419,20 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2363,22 +2450,22 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2393,12 +2480,12 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -2412,6 +2499,11 @@
         </is>
       </c>
       <c r="AV10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
         <is>
           <t>5일 일정이 빠듯해 쉬는 시간이 부족했음</t>
         </is>
@@ -2425,22 +2517,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2453,12 +2545,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2476,17 +2568,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2496,19 +2588,19 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2516,20 +2608,20 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2545,12 +2637,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2558,32 +2650,32 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2593,14 +2685,14 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2613,17 +2705,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2633,15 +2725,20 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2651,17 +2748,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2671,20 +2768,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2700,12 +2797,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2721,12 +2818,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2734,7 +2831,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2742,12 +2839,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2760,15 +2857,15 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2776,23 +2873,23 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2805,30 +2902,30 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2838,7 +2935,7 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
@@ -2852,6 +2949,11 @@
         </is>
       </c>
       <c r="AV12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
         <is>
           <t>식당 대기 시간이 길었음</t>
         </is>
@@ -2865,40 +2967,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2911,15 +3013,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2935,20 +3037,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2956,12 +3058,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2977,15 +3079,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2995,19 +3097,19 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3015,24 +3117,24 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AN13" t="inlineStr">
         <is>
           <t>보통</t>
@@ -3040,12 +3142,12 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -3060,7 +3162,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -3073,7 +3175,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3088,12 +3195,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3103,20 +3210,20 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3124,28 +3231,28 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -3153,20 +3260,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -3174,12 +3281,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3192,36 +3299,36 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AF14" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3229,7 +3336,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3237,20 +3344,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -3260,12 +3367,12 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -3275,15 +3382,20 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3293,17 +3405,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3313,20 +3425,20 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3334,41 +3446,41 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3381,18 +3493,18 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -3402,19 +3514,19 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3422,24 +3534,24 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3452,56 +3564,61 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3516,12 +3633,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3531,23 +3648,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3557,27 +3674,27 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -3587,14 +3704,14 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3610,36 +3727,36 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -3649,15 +3766,15 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3665,7 +3782,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3675,14 +3792,14 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3715,15 +3832,20 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
         <is>
           <t>식당 대기 시간이 길었음</t>
         </is>
@@ -3737,22 +3859,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3762,18 +3884,18 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3783,15 +3905,15 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3799,23 +3921,23 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3825,19 +3947,19 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3845,7 +3967,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -3855,14 +3977,14 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3870,20 +3992,20 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3899,53 +4021,58 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
         <is>
           <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
@@ -3959,17 +4086,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3979,7 +4106,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3987,12 +4114,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4005,23 +4132,23 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -4029,12 +4156,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4042,28 +4169,28 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -4071,12 +4198,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4084,20 +4211,20 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4105,43 +4232,43 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -4151,7 +4278,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -4159,7 +4286,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4169,17 +4301,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4197,15 +4329,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4215,18 +4347,18 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4239,12 +4371,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4257,19 +4389,19 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4287,14 +4419,14 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4307,15 +4439,15 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4333,37 +4465,37 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -4381,7 +4513,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4396,12 +4533,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4416,15 +4553,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4432,7 +4569,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -4440,20 +4577,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -4463,22 +4600,22 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -4488,80 +4625,80 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -4571,12 +4708,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -4586,7 +4723,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -4600,6 +4737,11 @@
         </is>
       </c>
       <c r="AV20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
         <is>
           <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
@@ -4613,44 +4755,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4668,14 +4810,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4691,12 +4833,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4712,20 +4854,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -4733,15 +4875,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -4751,36 +4893,36 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4788,7 +4930,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -4798,7 +4940,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -4808,20 +4950,25 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4836,17 +4983,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4856,19 +5003,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4884,12 +5031,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4905,20 +5052,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -4926,12 +5073,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4944,22 +5091,22 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -4972,15 +5119,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4990,15 +5137,15 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5011,12 +5158,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -5026,12 +5173,12 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -5040,6 +5187,11 @@
         </is>
       </c>
       <c r="AV22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
         <is>
           <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
@@ -5058,39 +5210,39 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5098,7 +5250,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -5108,14 +5260,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5123,7 +5275,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5131,15 +5283,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -5152,12 +5304,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5170,15 +5322,15 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5186,7 +5338,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -5194,12 +5346,12 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5207,61 +5359,66 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5271,17 +5428,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5291,28 +5448,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -5320,12 +5477,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5338,15 +5495,15 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5354,7 +5511,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -5362,12 +5519,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5380,15 +5537,15 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5401,18 +5558,18 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -5427,14 +5584,14 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AN24" t="inlineStr">
         <is>
           <t>보통</t>
@@ -5442,17 +5599,17 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -5462,7 +5619,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
@@ -5472,10 +5629,15 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AV24" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5485,17 +5647,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5510,18 +5672,18 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -5534,15 +5696,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -5552,18 +5714,18 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -5573,65 +5735,65 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5639,38 +5801,38 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -5680,20 +5842,25 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
         <is>
           <t>5일 일정이 빠듯해 쉬는 시간이 부족했음</t>
         </is>
@@ -5712,17 +5879,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5732,15 +5899,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5748,7 +5915,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -5756,33 +5923,33 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5790,7 +5957,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -5798,20 +5965,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -5819,33 +5986,33 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5861,15 +6028,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -5908,6 +6075,11 @@
         </is>
       </c>
       <c r="AV26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
         <is>
           <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
@@ -5921,22 +6093,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5951,17 +6123,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -5976,39 +6148,39 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6024,12 +6196,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6037,44 +6209,44 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6084,27 +6256,27 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -6119,17 +6291,17 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -6137,7 +6309,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6152,35 +6329,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>보통</t>
@@ -6188,23 +6365,23 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -6214,19 +6391,19 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6244,22 +6421,22 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -6267,33 +6444,33 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6301,7 +6478,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6309,45 +6486,45 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -6355,7 +6532,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
